--- a/measurements/27/Filled_2D_sections/sagittal/week27_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/27/Filled_2D_sections/sagittal/week27_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,57 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +551,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.599643069601428</v>
+        <v>2134.467120181406</v>
       </c>
       <c r="D2" t="n">
-        <v>11.68399310693508</v>
+        <v>228.116055897304</v>
       </c>
       <c r="E2" t="n">
-        <v>10.51469739762748</v>
+        <v>205.2869491917746</v>
       </c>
       <c r="F2" t="n">
         <v>1.111205835516621</v>
@@ -525,24 +570,45 @@
         <v>0.5154512831691427</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.739329268292683</v>
+        <v>1.329985119047619</v>
       </c>
       <c r="J2" t="n">
-        <v>0.739329268292683</v>
+        <v>14.43452380952381</v>
       </c>
       <c r="K2" t="n">
-        <v>0.739329268292683</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>7.120535714285714</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>14.43452380952381</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5.597098214285714</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.329985119047619</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>5.792593694229625</v>
+      <c r="X2" s="2" t="n">
+        <v>2208.015873015873</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +619,64 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.672516359309935</v>
+        <v>2162.244897959184</v>
       </c>
       <c r="D3" t="n">
-        <v>11.41396708314012</v>
+        <v>222.8441192422594</v>
       </c>
       <c r="E3" t="n">
-        <v>10.68124439948943</v>
+        <v>208.5385811328888</v>
       </c>
       <c r="F3" t="n">
         <v>1.068598999914815</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5471575415882061</v>
+        <v>0.5471575415882063</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7401867378048781</v>
+        <v>1.648065476190476</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7401867378048781</v>
+        <v>14.45126488095238</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7401867378048781</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>7.638888888888888</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14.45126488095238</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6.817336309523809</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.648065476190476</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>10.70010530425281</v>
+      <c r="X3" s="2" t="n">
+        <v>208.9068178449358</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +687,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.74390243902439</v>
+        <v>2189.455782312925</v>
       </c>
       <c r="D4" t="n">
-        <v>11.98259412079323</v>
+        <v>233.9458852154868</v>
       </c>
       <c r="E4" t="n">
-        <v>10.63246392331472</v>
+        <v>207.5862004075731</v>
       </c>
       <c r="F4" t="n">
         <v>1.126981874306477</v>
@@ -619,24 +706,45 @@
         <v>0.502707333569079</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7502858231707318</v>
+        <v>1.71875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7502858231707318</v>
+        <v>14.6484375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7502858231707318</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>7.98735119047619</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14.6484375</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7.594866071428571</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.71875</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>10.26825800712516</v>
+      <c r="X4" s="2" t="n">
+        <v>200.4755134724435</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +755,63 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.813206424747174</v>
+        <v>2215.873015873016</v>
       </c>
       <c r="D5" t="n">
-        <v>12.13485363925376</v>
+        <v>236.9185710520971</v>
       </c>
       <c r="E5" t="n">
-        <v>10.54327233244733</v>
+        <v>205.8448407763526</v>
       </c>
       <c r="F5" t="n">
         <v>1.150957051721814</v>
       </c>
       <c r="G5" t="n">
-        <v>0.496085489032252</v>
+        <v>0.4960854890322522</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.711985518292683</v>
+        <v>2.047991071428571</v>
       </c>
       <c r="J5" t="n">
-        <v>0.711985518292683</v>
+        <v>13.90066964285714</v>
       </c>
       <c r="K5" t="n">
-        <v>0.711985518292683</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>7.586805555555554</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13.90066964285714</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6.811755952380952</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.047991071428571</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="X5" s="2" t="n">
         <v>1.041504844914065</v>
       </c>
     </row>
@@ -694,34 +823,64 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.941106484235575</v>
+        <v>2264.625850340136</v>
       </c>
       <c r="D6" t="n">
-        <v>10.81921646071643</v>
+        <v>211.2323213758923</v>
       </c>
       <c r="E6" t="n">
-        <v>10.46591693017541</v>
+        <v>204.334568636758</v>
       </c>
       <c r="F6" t="n">
-        <v>1.033757150271506</v>
+        <v>1.033757150271505</v>
       </c>
       <c r="G6" t="n">
         <v>0.6378015653405393</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.079613095238095</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.503720238095237</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.517733134920635</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7.503720238095237</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.969866071428571</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.079613095238095</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.6413575721544404</v>
+      <c r="X6" s="2" t="n">
+        <v>0.6413575721544406</v>
       </c>
     </row>
     <row r="7">
@@ -732,34 +891,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.952706722189173</v>
+        <v>2269.047619047619</v>
       </c>
       <c r="D7" t="n">
-        <v>10.81329835333475</v>
+        <v>211.1167773746309</v>
       </c>
       <c r="E7" t="n">
-        <v>10.49449181847456</v>
+        <v>204.8924593130747</v>
       </c>
       <c r="F7" t="n">
         <v>1.030378463328635</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6397465881986596</v>
+        <v>0.6397465881986598</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.047991071428571</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7.198660714285714</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.302579365079365</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7.198660714285714</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6.661086309523809</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.047991071428571</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.2</v>
+      <c r="X7" s="2" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -770,34 +959,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.949137418203451</v>
+        <v>2267.687074829932</v>
       </c>
       <c r="D8" t="n">
-        <v>10.69553185672295</v>
+        <v>208.8175267264956</v>
       </c>
       <c r="E8" t="n">
-        <v>10.40530027703541</v>
+        <v>203.1511006468818</v>
       </c>
       <c r="F8" t="n">
         <v>1.027892667386839</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6535203167559277</v>
+        <v>0.6535203167559276</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.173735119047619</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6.744791666666666</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.007626488095238</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6.744791666666666</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6.322544642857142</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.789434523809524</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.173735119047619</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.7354468368902439</v>
+      <c r="X8" s="2" t="n">
+        <v>1.87007068452381</v>
       </c>
     </row>
     <row r="9">
@@ -808,34 +1030,67 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.949137418203451</v>
+        <v>2267.687074829932</v>
       </c>
       <c r="D9" t="n">
-        <v>10.69553185672295</v>
+        <v>208.8175267264956</v>
       </c>
       <c r="E9" t="n">
-        <v>10.40530027703541</v>
+        <v>203.1511006468818</v>
       </c>
       <c r="F9" t="n">
         <v>1.027892667386839</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6535203167559277</v>
+        <v>0.6535203167559276</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.173735119047619</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.744791666666666</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.007626488095238</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6.744791666666666</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6.322544642857142</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.789434523809524</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.173735119047619</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.7354468368902439</v>
+      <c r="X9" s="2" t="n">
+        <v>7.974981398809523</v>
       </c>
     </row>
     <row r="10">
@@ -846,17 +1101,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.937537180249851</v>
+        <v>2263.265306122449</v>
       </c>
       <c r="D10" t="n">
-        <v>10.62062776379469</v>
+        <v>207.3551134836106</v>
       </c>
       <c r="E10" t="n">
-        <v>10.41958774880665</v>
+        <v>203.4300465243203</v>
       </c>
       <c r="F10" t="n">
         <v>1.019294430819594</v>
@@ -865,15 +1120,45 @@
         <v>0.6614786488471128</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.789434523809524</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6.272321428571428</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.74578373015873</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6.272321428571428</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6.175595238095238</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.789434523809524</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.7354468368902439</v>
+      <c r="X10" s="2" t="n">
+        <v>4.808609250992063</v>
       </c>
     </row>
     <row r="11">
@@ -884,17 +1169,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.919095776323617</v>
+        <v>2256.235827664399</v>
       </c>
       <c r="D11" t="n">
-        <v>10.62062776088715</v>
+        <v>207.3551134268443</v>
       </c>
       <c r="E11" t="n">
-        <v>10.37917666900449</v>
+        <v>202.6410682996114</v>
       </c>
       <c r="F11" t="n">
         <v>1.023263029388806</v>
@@ -903,7 +1188,48 @@
         <v>0.6594241618707989</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.329985119047619</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.075148809523809</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.849516369047619</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6.075148809523809</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5.803571428571428</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.189360119047619</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.329985119047619</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -914,26 +1240,67 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.897977394408091</v>
+        <v>2248.185941043084</v>
       </c>
       <c r="D12" t="n">
-        <v>10.54572367958906</v>
+        <v>205.8927004110245</v>
       </c>
       <c r="E12" t="n">
-        <v>10.33876560664758</v>
+        <v>201.8520904155004</v>
       </c>
       <c r="F12" t="n">
         <v>1.020017677236866</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6664386750355984</v>
+        <v>0.6664386750355983</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.186755952380952</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.941220238095238</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.712797619047619</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5.941220238095238</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.008928571428571</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.186755952380952</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>14.35872395833333</v>
       </c>
     </row>
     <row r="13">
@@ -944,17 +1311,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.873884592504462</v>
+        <v>2239.002267573696</v>
       </c>
       <c r="D13" t="n">
-        <v>10.47081959247589</v>
+        <v>204.4302872816722</v>
       </c>
       <c r="E13" t="n">
-        <v>10.26977958911803</v>
+        <v>200.5052205494472</v>
       </c>
       <c r="F13" t="n">
         <v>1.019575882969376</v>
@@ -963,7 +1330,45 @@
         <v>0.6732462135618656</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.442336309523809</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.734747023809524</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.312996031746032</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5.734747023809524</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.442336309523809</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
@@ -974,17 +1379,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.836406900654373</v>
+        <v>2224.716553287982</v>
       </c>
       <c r="D14" t="n">
-        <v>10.353053090049</v>
+        <v>202.1310365200043</v>
       </c>
       <c r="E14" t="n">
-        <v>10.18058803023362</v>
+        <v>198.7638615426563</v>
       </c>
       <c r="F14" t="n">
         <v>1.01694057939514</v>
@@ -993,7 +1398,45 @@
         <v>0.684255889549733</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.198660714285714</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.483630952380952</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.830605158730158</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5.483630952380952</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.198660714285714</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>6.444289434523808</v>
       </c>
     </row>
     <row r="15">
@@ -1004,17 +1447,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.836406900654373</v>
+        <v>2224.716553287982</v>
       </c>
       <c r="D15" t="n">
-        <v>10.353053090049</v>
+        <v>202.1310365200043</v>
       </c>
       <c r="E15" t="n">
-        <v>10.18058803023362</v>
+        <v>198.7638615426563</v>
       </c>
       <c r="F15" t="n">
         <v>1.01694057939514</v>
@@ -1023,7 +1466,45 @@
         <v>0.684255889549733</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.198660714285714</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.483630952380952</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.830605158730158</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5.483630952380952</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.198660714285714</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>5.635044642857142</v>
       </c>
     </row>
     <row r="16">
@@ -1034,26 +1515,64 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.792385484830458</v>
+        <v>2207.936507936508</v>
       </c>
       <c r="D16" t="n">
-        <v>10.21508104626725</v>
+        <v>199.4372966175987</v>
       </c>
       <c r="E16" t="n">
-        <v>10.07119092999435</v>
+        <v>196.6280133951278</v>
       </c>
       <c r="F16" t="n">
-        <v>1.014287299016879</v>
+        <v>1.014287299016878</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6975634023255007</v>
+        <v>0.6975634023255011</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.416294642857143</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.340401785714286</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.644593253968254</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5.340401785714286</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.177083333333333</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.416294642857143</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="17">
@@ -1064,17 +1583,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.743010113027959</v>
+        <v>2189.115646258503</v>
       </c>
       <c r="D17" t="n">
-        <v>10.14609501129243</v>
+        <v>198.0904264109475</v>
       </c>
       <c r="E17" t="n">
-        <v>10.01404101964904</v>
+        <v>195.5122294312432</v>
       </c>
       <c r="F17" t="n">
         <v>1.013186883435397</v>
@@ -1083,7 +1602,45 @@
         <v>0.7010541997066253</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.219122023809524</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.805431547619047</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.654513888888889</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5.805431547619047</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.938988095238095</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.219122023809524</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>2.176153273809524</v>
       </c>
     </row>
     <row r="18">
@@ -1094,26 +1651,64 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.689767995240929</v>
+        <v>2168.820861678004</v>
       </c>
       <c r="D18" t="n">
-        <v>10.1805880156959</v>
+        <v>198.7638612588246</v>
       </c>
       <c r="E18" t="n">
-        <v>9.973629939846877</v>
+        <v>194.7232512065342</v>
       </c>
       <c r="F18" t="n">
         <v>1.020750526849024</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6898563976024491</v>
+        <v>0.6898563976024492</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.455357142857143</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.309523809523809</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.814484126984127</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6.309523809523809</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.678571428571428</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.455357142857143</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>1.78999255952381</v>
       </c>
     </row>
     <row r="19">
@@ -1124,25 +1719,63 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.624925639500297</v>
+        <v>2144.104308390023</v>
       </c>
       <c r="D19" t="n">
-        <v>10.06282149873129</v>
+        <v>196.4646102133251</v>
       </c>
       <c r="E19" t="n">
-        <v>9.890356438915905</v>
+        <v>193.0974352359772</v>
       </c>
       <c r="F19" t="n">
         <v>1.01743769912445</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6980509326219211</v>
+        <v>0.6980509326219213</v>
       </c>
       <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.020089285714286</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.635044642857142</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.781001984126984</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>6.635044642857142</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.687872023809524</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.020089285714286</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1154,25 +1787,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.539559785841761</v>
+        <v>2111.56462585034</v>
       </c>
       <c r="D20" t="n">
-        <v>10.09731452930264</v>
+        <v>197.1380455720992</v>
       </c>
       <c r="E20" t="n">
-        <v>9.752384392226615</v>
+        <v>190.4036952768053</v>
       </c>
       <c r="F20" t="n">
-        <v>1.03536880040854</v>
+        <v>1.035368800408541</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6827682990038688</v>
+        <v>0.6827682990038685</v>
       </c>
       <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.962425595238095</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.395833333333333</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.913070436507936</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>7.395833333333333</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.380952380952381</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.962425595238095</v>
+      </c>
+      <c r="T20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1184,25 +1847,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.539559785841761</v>
+        <v>2111.56462585034</v>
       </c>
       <c r="D21" t="n">
-        <v>10.09731452930264</v>
+        <v>197.1380455720992</v>
       </c>
       <c r="E21" t="n">
-        <v>9.752384392226615</v>
+        <v>190.4036952768053</v>
       </c>
       <c r="F21" t="n">
-        <v>1.03536880040854</v>
+        <v>1.035368800408541</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6827682990038688</v>
+        <v>0.6827682990038685</v>
       </c>
       <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.962425595238095</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.395833333333333</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.913070436507936</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>7.395833333333333</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.380952380952381</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.962425595238095</v>
+      </c>
+      <c r="T21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1213,7 +1906,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1236,6 +1929,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/27/Filled_2D_sections/sagittal/week27_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/27/Filled_2D_sections/sagittal/week27_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1966,4 +2172,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week27_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2208.015873015873</v>
+      </c>
+      <c r="D10" t="n">
+        <v>53.82946241198835</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2111.56462585034</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2269.047619047619</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>208.9068178449358</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12.25236545897869</v>
+      </c>
+      <c r="E11" t="n">
+        <v>196.4646102133251</v>
+      </c>
+      <c r="F11" t="n">
+        <v>236.9185710520971</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.041504844914065</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.04041642368114438</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.013186883435397</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.150957051721814</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6413575721544404</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.06772292686246537</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4960854890322522</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7010541997066253</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0131.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0133.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0135.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0137.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.4103913408340616</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4103913408340617</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.512989176042577</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.512989176042577</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14.35872395833333</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.320446111928922</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.90066964285714</v>
+      </c>
+      <c r="F48" t="n">
+        <v>14.6484375</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>30</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.17454117063492</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.9531802230576403</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7.594866071428571</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>30</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.047433035714286</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5064268920435872</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.173735119047619</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.177083333333333</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>